--- a/Raw Data/Micro Plans/November 2025/Micro Plan - TA-506 Nov'25.xlsx
+++ b/Raw Data/Micro Plans/November 2025/Micro Plan - TA-506 Nov'25.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DPR\TA-506\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushikb\Documents\Work\Git\Office-work-\Raw Data\Micro Plans\November 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B7DF08-EEC7-4138-AC3F-1242160BC8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A65CE73B-AA6B-4C25-AE8C-37ED6E9E1121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="757" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="757" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FDN-June25" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Stub dispatch" sheetId="4" state="hidden" r:id="rId2"/>
     <sheet name="Erection-Nov25" sheetId="2" r:id="rId3"/>
-    <sheet name="Stringing- Nov25 " sheetId="6" r:id="rId4"/>
-    <sheet name="STG-Sep25" sheetId="3" state="hidden" r:id="rId5"/>
+    <sheet name="STG-Sep25" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Erection-Nov25'!$B$1:$H$72</definedName>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="222">
   <si>
     <t>Project Code</t>
   </si>
@@ -409,78 +408,6 @@
   </si>
   <si>
     <t>16/0</t>
-  </si>
-  <si>
-    <t>Name of the line : 765 KV D/C Bikaner III - Neemrana II TL02</t>
-  </si>
-  <si>
-    <t>Powergrid Bikaner Neemrana Transmission Limited (Power Grid Corporation of India)</t>
-  </si>
-  <si>
-    <t>Executing Agency:- KEC International Limited</t>
-  </si>
-  <si>
-    <t>Datewise Stringing planning for the month of November 2025</t>
-  </si>
-  <si>
-    <t>Sr no</t>
-  </si>
-  <si>
-    <t>Section Name</t>
-  </si>
-  <si>
-    <t>Tower Erection  Status</t>
-  </si>
-  <si>
-    <t>Tower in section</t>
-  </si>
-  <si>
-    <t>Insulator Hoisting</t>
-  </si>
-  <si>
-    <t>Paying Out Start</t>
-  </si>
-  <si>
-    <t>Paying Out Completed</t>
-  </si>
-  <si>
-    <t>Final sag complete</t>
-  </si>
-  <si>
-    <t>AP-6 - AP-7/0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Complete </t>
-  </si>
-  <si>
-    <t>Rahim Khan</t>
-  </si>
-  <si>
-    <t>AP-5 - AP-5A/0</t>
-  </si>
-  <si>
-    <t>AP-5A/0 - AP-6</t>
-  </si>
-  <si>
-    <t>AP-32A/0 - AP-33/0</t>
-  </si>
-  <si>
-    <t>Tanjira Bibi</t>
-  </si>
-  <si>
-    <t>AP-32/0 - AP-32A/0</t>
-  </si>
-  <si>
-    <t>AP-33/0 - AP-34/0</t>
-  </si>
-  <si>
-    <t>Total length (KM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Micro Plan - Stringing </t>
-  </si>
-  <si>
-    <t>Section Length Miter</t>
   </si>
   <si>
     <t>1/8</t>
@@ -791,17 +718,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="167" formatCode="[$-409]d/mmm/yy;@"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="#,##0.000"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="167" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="168" formatCode="[$-409]d/mmm/yy;@"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="#,##0.000"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="172" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1012,12 +939,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Verdana"/>
@@ -1043,7 +964,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1109,14 +1030,8 @@
         <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="30">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1319,205 +1234,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
@@ -1536,21 +1263,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1570,13 +1297,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
@@ -1648,11 +1375,11 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1695,36 +1422,36 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1768,13 +1495,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1783,25 +1510,25 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1810,31 +1537,31 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1843,13 +1570,13 @@
     <xf numFmtId="17" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1864,7 +1591,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -1879,41 +1606,41 @@
     <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="1" fontId="17" fillId="6" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="6" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="6" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1941,7 +1668,7 @@
     <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="8" borderId="3" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="18" fillId="8" borderId="3" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1954,7 +1681,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1978,16 +1705,16 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1999,16 +1726,16 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2020,7 +1747,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2059,19 +1786,19 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2080,7 +1807,7 @@
     <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2089,7 +1816,7 @@
     <xf numFmtId="2" fontId="26" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2128,10 +1855,10 @@
     <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="23" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2164,16 +1891,16 @@
     <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="12" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="28" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2185,71 +1912,66 @@
     <xf numFmtId="15" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="29" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2265,51 +1987,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2325,77 +2002,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="20" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="1" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="19" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="16" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="28" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="18" xfId="78" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="29" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="172">
@@ -2572,17 +2189,7 @@
     <cellStyle name="Percent 4" xfId="124" xr:uid="{32CBB0B0-D0C8-46CB-AD6B-26DAB717BBAE}"/>
     <cellStyle name="TableStyleLight1" xfId="119" xr:uid="{0B733BF9-52ED-40EC-B19D-44B5DCCD51EC}"/>
   </cellStyles>
-  <dxfs count="87">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="65">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -2655,216 +2262,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3983,137 +3380,137 @@
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="181" t="s">
+      <c r="A18" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="181" t="s">
+      <c r="B18" s="178" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="178" t="s">
+      <c r="C18" s="174" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="181" t="s">
+      <c r="D18" s="178" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="178" t="s">
+      <c r="E18" s="174" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="178" t="s">
+      <c r="F18" s="174" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="181" t="s">
+      <c r="G18" s="178" t="s">
         <v>8</v>
       </c>
-      <c r="H18" s="193" t="s">
+      <c r="H18" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="193"/>
-      <c r="J18" s="193"/>
-      <c r="K18" s="193"/>
-      <c r="L18" s="193"/>
-      <c r="M18" s="193"/>
-      <c r="N18" s="193"/>
-      <c r="O18" s="193"/>
-      <c r="P18" s="186" t="s">
+      <c r="I18" s="165"/>
+      <c r="J18" s="165"/>
+      <c r="K18" s="165"/>
+      <c r="L18" s="165"/>
+      <c r="M18" s="165"/>
+      <c r="N18" s="165"/>
+      <c r="O18" s="165"/>
+      <c r="P18" s="168" t="s">
         <v>19</v>
       </c>
-      <c r="R18" s="178" t="s">
+      <c r="R18" s="174" t="s">
         <v>36</v>
       </c>
-      <c r="T18" s="187" t="s">
+      <c r="T18" s="169" t="s">
         <v>31</v>
       </c>
-      <c r="U18" s="188"/>
-      <c r="V18" s="188"/>
-      <c r="W18" s="188"/>
-      <c r="X18" s="188"/>
-      <c r="Y18" s="189"/>
-      <c r="AA18" s="187" t="s">
+      <c r="U18" s="170"/>
+      <c r="V18" s="170"/>
+      <c r="W18" s="170"/>
+      <c r="X18" s="170"/>
+      <c r="Y18" s="171"/>
+      <c r="AA18" s="169" t="s">
         <v>30</v>
       </c>
-      <c r="AB18" s="188"/>
-      <c r="AC18" s="188"/>
-      <c r="AD18" s="188"/>
-      <c r="AE18" s="188"/>
-      <c r="AF18" s="189"/>
-      <c r="AG18" s="190" t="s">
+      <c r="AB18" s="170"/>
+      <c r="AC18" s="170"/>
+      <c r="AD18" s="170"/>
+      <c r="AE18" s="170"/>
+      <c r="AF18" s="171"/>
+      <c r="AG18" s="172" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:33" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="182"/>
-      <c r="B19" s="182"/>
-      <c r="C19" s="179"/>
-      <c r="D19" s="182"/>
-      <c r="E19" s="179"/>
-      <c r="F19" s="179"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="198" t="s">
+      <c r="A19" s="179"/>
+      <c r="B19" s="179"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="179"/>
+      <c r="E19" s="176"/>
+      <c r="F19" s="176"/>
+      <c r="G19" s="179"/>
+      <c r="H19" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="I19" s="198"/>
-      <c r="J19" s="198" t="s">
+      <c r="I19" s="164"/>
+      <c r="J19" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="K19" s="198"/>
-      <c r="L19" s="198" t="s">
+      <c r="K19" s="164"/>
+      <c r="L19" s="164" t="s">
         <v>13</v>
       </c>
-      <c r="M19" s="198"/>
-      <c r="N19" s="194" t="s">
+      <c r="M19" s="164"/>
+      <c r="N19" s="162" t="s">
         <v>15</v>
       </c>
-      <c r="O19" s="194" t="s">
+      <c r="O19" s="162" t="s">
         <v>14</v>
       </c>
-      <c r="P19" s="186"/>
-      <c r="R19" s="192"/>
-      <c r="T19" s="184" t="s">
+      <c r="P19" s="168"/>
+      <c r="R19" s="175"/>
+      <c r="T19" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="U19" s="184" t="s">
+      <c r="U19" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="V19" s="184" t="s">
+      <c r="V19" s="166" t="s">
         <v>26</v>
       </c>
-      <c r="W19" s="184" t="s">
+      <c r="W19" s="166" t="s">
         <v>27</v>
       </c>
-      <c r="X19" s="184" t="s">
+      <c r="X19" s="166" t="s">
         <v>28</v>
       </c>
       <c r="Y19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AA19" s="184" t="s">
+      <c r="AA19" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="AB19" s="184" t="s">
+      <c r="AB19" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="AC19" s="184" t="s">
+      <c r="AC19" s="166" t="s">
         <v>26</v>
       </c>
-      <c r="AD19" s="184" t="s">
+      <c r="AD19" s="166" t="s">
         <v>27</v>
       </c>
-      <c r="AE19" s="184" t="s">
+      <c r="AE19" s="166" t="s">
         <v>28</v>
       </c>
       <c r="AF19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AG19" s="191"/>
+      <c r="AG19" s="173"/>
     </row>
     <row r="20" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="183"/>
-      <c r="B20" s="182"/>
-      <c r="C20" s="179"/>
-      <c r="D20" s="182"/>
-      <c r="E20" s="180"/>
-      <c r="F20" s="180"/>
-      <c r="G20" s="182"/>
+      <c r="A20" s="180"/>
+      <c r="B20" s="179"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="179"/>
+      <c r="E20" s="177"/>
+      <c r="F20" s="177"/>
+      <c r="G20" s="179"/>
       <c r="H20" s="93" t="s">
         <v>10</v>
       </c>
@@ -4132,25 +3529,25 @@
       <c r="M20" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="N20" s="195"/>
-      <c r="O20" s="195"/>
+      <c r="N20" s="163"/>
+      <c r="O20" s="163"/>
       <c r="P20" s="44" t="s">
         <v>50</v>
       </c>
       <c r="R20" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="T20" s="185"/>
-      <c r="U20" s="185"/>
-      <c r="V20" s="185"/>
-      <c r="W20" s="185"/>
-      <c r="X20" s="185"/>
+      <c r="T20" s="167"/>
+      <c r="U20" s="167"/>
+      <c r="V20" s="167"/>
+      <c r="W20" s="167"/>
+      <c r="X20" s="167"/>
       <c r="Y20" s="19"/>
-      <c r="AA20" s="185"/>
-      <c r="AB20" s="185"/>
-      <c r="AC20" s="185"/>
-      <c r="AD20" s="185"/>
-      <c r="AE20" s="185"/>
+      <c r="AA20" s="167"/>
+      <c r="AB20" s="167"/>
+      <c r="AC20" s="167"/>
+      <c r="AD20" s="167"/>
+      <c r="AE20" s="167"/>
       <c r="AF20" s="19" t="s">
         <v>50</v>
       </c>
@@ -4421,7 +3818,7 @@
       <c r="D25" s="85"/>
       <c r="E25" s="100"/>
       <c r="F25" s="8"/>
-      <c r="G25" s="196"/>
+      <c r="G25" s="160"/>
       <c r="H25" s="98"/>
       <c r="I25" s="98"/>
       <c r="J25" s="98"/>
@@ -4479,7 +3876,7 @@
       <c r="D26" s="8"/>
       <c r="E26" s="101"/>
       <c r="F26" s="96"/>
-      <c r="G26" s="197"/>
+      <c r="G26" s="161"/>
       <c r="H26" s="98"/>
       <c r="I26" s="98"/>
       <c r="J26" s="98"/>
@@ -4834,16 +4231,13 @@
     <filterColumn colId="13" showButton="0"/>
   </autoFilter>
   <mergeCells count="29">
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="H18:O18"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="U19:U20"/>
-    <mergeCell ref="V19:V20"/>
-    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
     <mergeCell ref="X19:X20"/>
     <mergeCell ref="P18:P19"/>
     <mergeCell ref="AA18:AF18"/>
@@ -4856,162 +4250,165 @@
     <mergeCell ref="R18:R19"/>
     <mergeCell ref="T18:Y18"/>
     <mergeCell ref="T19:T20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="H18:O18"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="U19:U20"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="B21">
-    <cfRule type="duplicateValues" dxfId="86" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="4"/>
-    <cfRule type="expression" dxfId="82" priority="5" stopIfTrue="1">
+    <cfRule type="duplicateValues" dxfId="64" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="4"/>
+    <cfRule type="expression" dxfId="60" priority="5" stopIfTrue="1">
       <formula>AND(COUNTIF($D$28:$D$37, B21)+COUNTIF($D$16:$D$16, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="6" stopIfTrue="1">
       <formula>AND(COUNTIF($D$28:$D$65380, B21)+COUNTIF($D$1:$D$16, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="7" stopIfTrue="1">
       <formula>AND(COUNTIF($D$17:$D$65380, B21)+COUNTIF($D$1:$D$16, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="8" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$123, B21)+COUNTIF($D$142:$D$65380, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="9" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B21)+COUNTIF($D$214:$D$65380, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="10" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="10" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B21)+COUNTIF($D$214:$D$65380, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="11" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="11" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B21)+COUNTIF($D$214:$D$65380, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="12" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="12" stopIfTrue="1">
       <formula>AND(COUNTIF($D$474:$D$65380, B21)+COUNTIF($D$454:$D$455, B21)+COUNTIF($D$416:$D$417, B21)+COUNTIF($D$374:$D$377, B21)+COUNTIF($D$351:$D$352, B21)+COUNTIF($D$324:$D$325, B21)+COUNTIF($D$303:$D$303, B21)+COUNTIF($D$288:$D$289, B21)+COUNTIF($D$263:$D$263, B21)+COUNTIF($D$252:$D$253, B21)+COUNTIF($D$233:$D$234, B21)+COUNTIF($D$51:$D$218, B21)+COUNTIF($D$219:$D$220, B21)+COUNTIF($D$1:$D$50, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21:B27">
-    <cfRule type="duplicateValues" dxfId="74" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="duplicateValues" dxfId="73" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="duplicateValues" dxfId="70" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="20"/>
-    <cfRule type="expression" dxfId="68" priority="1251" stopIfTrue="1">
+    <cfRule type="duplicateValues" dxfId="48" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="20"/>
+    <cfRule type="expression" dxfId="46" priority="1251" stopIfTrue="1">
       <formula>AND(COUNTIF($C$2:$C$65291, B23)+COUNTIF(#REF!, B23)&gt;1,NOT(ISBLANK(B23)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="1252" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="1252" stopIfTrue="1">
       <formula>AND(COUNTIF($C$145:$C$65291, B23)+COUNTIF($C$125:$C$126, B23)+COUNTIF($C$87:$C$88, B23)+COUNTIF($C$45:$C$48, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF(#REF!, B23)+COUNTIF($B$9:$B$9, B23)+COUNTIF($C$2:$C$8, B23)&gt;1,NOT(ISBLANK(B23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27 B21 B23">
-    <cfRule type="expression" dxfId="66" priority="1248" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="1248" stopIfTrue="1">
       <formula>AND(COUNTIF($C$1:$C$65282, B21)+COUNTIF(#REF!, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27 B23 B21">
-    <cfRule type="expression" dxfId="65" priority="1236" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="1236" stopIfTrue="1">
       <formula>AND(COUNTIF($C$136:$C$65282, B21)+COUNTIF($C$116:$C$117, B21)+COUNTIF($C$78:$C$79, B21)+COUNTIF($C$36:$C$39, B21)+COUNTIF($C$23:$C$24, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF(#REF!, B21)+COUNTIF($C$1:$C$5, B21)&gt;1,NOT(ISBLANK(B21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:B27">
-    <cfRule type="duplicateValues" dxfId="64" priority="1239"/>
-    <cfRule type="expression" dxfId="63" priority="1240" stopIfTrue="1">
+    <cfRule type="duplicateValues" dxfId="42" priority="1239"/>
+    <cfRule type="expression" dxfId="41" priority="1240" stopIfTrue="1">
       <formula>AND(COUNTIF($D$28:$D$37, B26)+COUNTIF($D$16:$D$16, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="1241" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="1241" stopIfTrue="1">
       <formula>AND(COUNTIF($D$28:$D$65380, B26)+COUNTIF($D$1:$D$16, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="1242" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="1242" stopIfTrue="1">
       <formula>AND(COUNTIF($D$17:$D$65380, B26)+COUNTIF($D$1:$D$16, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="1243" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="1243" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$123, B26)+COUNTIF($D$142:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="1245" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="1245" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="1246" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="1246" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="1247" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="1247" stopIfTrue="1">
       <formula>AND(COUNTIF($D$474:$D$65380, B26)+COUNTIF($D$454:$D$455, B26)+COUNTIF($D$416:$D$417, B26)+COUNTIF($D$374:$D$377, B26)+COUNTIF($D$351:$D$352, B26)+COUNTIF($D$324:$D$325, B26)+COUNTIF($D$303:$D$303, B26)+COUNTIF($D$288:$D$289, B26)+COUNTIF($D$263:$D$263, B26)+COUNTIF($D$252:$D$253, B26)+COUNTIF($D$233:$D$234, B26)+COUNTIF($D$51:$D$218, B26)+COUNTIF($D$219:$D$220, B26)+COUNTIF($D$1:$D$50, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="1244" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="1244" stopIfTrue="1">
       <formula>AND(COUNTIF($D$1:$D$191, B26)+COUNTIF($D$214:$D$65380, B26)&gt;1,NOT(ISBLANK(B26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="duplicateValues" dxfId="55" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="52" priority="1190"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="1191"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="1192"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1191"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29:B1048576 B1:B20">
-    <cfRule type="duplicateValues" dxfId="49" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L4">
-    <cfRule type="expression" dxfId="48" priority="1221" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="1221" stopIfTrue="1">
       <formula>AND(COUNTIF($C$1:$C$65460, L4)+COUNTIF(#REF!, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="1220" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="1220" stopIfTrue="1">
       <formula>AND(COUNTIF($C$314:$C$65460, L4)+COUNTIF($C$294:$C$295, L4)+COUNTIF($C$256:$C$257, L4)+COUNTIF($C$214:$C$217, L4)+COUNTIF($C$191:$C$192, L4)+COUNTIF($C$164:$C$165, L4)+COUNTIF($C$143:$C$143, L4)+COUNTIF($C$128:$C$129, L4)+COUNTIF($C$103:$C$103, L4)+COUNTIF($C$92:$C$93, L4)+COUNTIF($C$73:$C$74, L4)+COUNTIF($C$29:$C$56, L4)+COUNTIF($C$58:$C$60, L4)+COUNTIF($C$1:$C$27, L4)&gt;1,NOT(ISBLANK(L4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M4">
-    <cfRule type="expression" dxfId="46" priority="1223" stopIfTrue="1">
+    <cfRule type="expression" dxfId="24" priority="1223" stopIfTrue="1">
       <formula>AND(COUNTIF($D$314:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="1224" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="1224" stopIfTrue="1">
       <formula>AND(COUNTIF($D$294:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="1225" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="1225" stopIfTrue="1">
       <formula>AND(COUNTIF($D$256:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="1226" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="1226" stopIfTrue="1">
       <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="1227" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="1227" stopIfTrue="1">
       <formula>AND(COUNTIF($D$214:$D$65460, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="1228" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="1228" stopIfTrue="1">
       <formula>AND(COUNTIF($D$191:$D$65460, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$51:$D$51, M4)+COUNTIF($D$53:$D$60, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="1229" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="1229" stopIfTrue="1">
       <formula>AND(COUNTIF($F$369:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$352:$F$353, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="1230" stopIfTrue="1">
+    <cfRule type="expression" dxfId="17" priority="1230" stopIfTrue="1">
       <formula>AND(COUNTIF($F$352:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$332:$F$333, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="1231" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="1231" stopIfTrue="1">
       <formula>AND(COUNTIF($F$332:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$294:$F$295, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="1232" stopIfTrue="1">
+    <cfRule type="expression" dxfId="15" priority="1232" stopIfTrue="1">
       <formula>AND(COUNTIF($F$294:$F$65454, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$252:$F$255, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="1233" stopIfTrue="1">
+    <cfRule type="expression" dxfId="14" priority="1233" stopIfTrue="1">
       <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$96:$F$98, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="1234" stopIfTrue="1">
+    <cfRule type="expression" dxfId="13" priority="1234" stopIfTrue="1">
       <formula>AND(COUNTIF($F$252:$F$65454, M4)+COUNTIF($F$229:$F$230, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="1235" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="1235" stopIfTrue="1">
       <formula>AND(COUNTIF($F$229:$F$65454, M4)+COUNTIF($F$202:$F$203, M4)+COUNTIF($F$181:$F$181, M4)+COUNTIF($F$166:$F$167, M4)+COUNTIF($F$1:$F$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$141:$F$141, M4)+COUNTIF($F$130:$F$131, M4)+COUNTIF(#REF!, M4)+COUNTIF($F$111:$F$112, M4)+COUNTIF($F$89:$F$89, M4)+COUNTIF($F$91:$F$98, M4)+COUNTIF(#REF!, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="1222" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="1222" stopIfTrue="1">
       <formula>AND(COUNTIF($D$331:$D$65460, M4)+COUNTIF($D$1:$D$27, M4)+COUNTIF(#REF!, M4)+COUNTIF($D$314:$D$315, M4)+COUNTIF($D$294:$D$295, M4)+COUNTIF($D$256:$D$257, M4)+COUNTIF($D$214:$D$217, M4)+COUNTIF($D$191:$D$192, M4)+COUNTIF($D$164:$D$165, M4)+COUNTIF($D$143:$D$143, M4)+COUNTIF($D$128:$D$129, M4)+COUNTIF($D$103:$D$103, M4)+COUNTIF($D$92:$D$93, M4)+COUNTIF($D$73:$D$74, M4)+COUNTIF($D$58:$D$60, M4)&gt;1,NOT(ISBLANK(M4)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5133,7 +4530,7 @@
       <c r="Q4" s="70">
         <v>0</v>
       </c>
-      <c r="R4" s="199" t="s">
+      <c r="R4" s="181" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5176,14 +4573,14 @@
       <c r="Q5" s="70">
         <v>0</v>
       </c>
-      <c r="R5" s="200"/>
+      <c r="R5" s="182"/>
     </row>
     <row r="6" spans="2:18" s="75" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="201" t="s">
+      <c r="B6" s="183" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="202"/>
-      <c r="D6" s="203"/>
+      <c r="C6" s="184"/>
+      <c r="D6" s="185"/>
       <c r="E6" s="73">
         <v>160</v>
       </c>
@@ -5210,7 +4607,7 @@
     <mergeCell ref="B6:D6"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E5">
-    <cfRule type="containsText" dxfId="32" priority="1" operator="containsText" text="proto">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="proto">
       <formula>NOT(ISERROR(SEARCH("proto",E4)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5312,21 +4709,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D2" s="224">
+        <v>122</v>
+      </c>
+      <c r="D2" s="156">
         <v>17.633662000000001</v>
       </c>
-      <c r="E2" s="226"/>
+      <c r="E2" s="158"/>
       <c r="F2" s="136"/>
       <c r="G2" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H2" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I2" s="137"/>
       <c r="J2" s="138"/>
@@ -5334,7 +4731,7 @@
       <c r="L2" s="132"/>
       <c r="M2" s="138"/>
       <c r="N2" s="138"/>
-      <c r="O2" s="225">
+      <c r="O2" s="157">
         <f>D2*13433</f>
         <v>236872.981646</v>
       </c>
@@ -5346,21 +4743,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="224">
+        <v>122</v>
+      </c>
+      <c r="D3" s="156">
         <v>17.633662000000001</v>
       </c>
-      <c r="E3" s="226"/>
+      <c r="E3" s="158"/>
       <c r="F3" s="136"/>
       <c r="G3" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H3" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I3" s="137"/>
       <c r="J3" s="138"/>
@@ -5368,7 +4765,7 @@
       <c r="L3" s="132"/>
       <c r="M3" s="138"/>
       <c r="N3" s="138"/>
-      <c r="O3" s="225">
+      <c r="O3" s="157">
         <f t="shared" ref="O3:O66" si="0">D3*13433</f>
         <v>236872.981646</v>
       </c>
@@ -5396,21 +4793,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" s="224">
+        <v>122</v>
+      </c>
+      <c r="D4" s="156">
         <v>17.633662000000001</v>
       </c>
-      <c r="E4" s="226"/>
+      <c r="E4" s="158"/>
       <c r="F4" s="136"/>
       <c r="G4" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H4" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I4" s="137"/>
       <c r="J4" s="138"/>
@@ -5418,7 +4815,7 @@
       <c r="L4" s="132"/>
       <c r="M4" s="138"/>
       <c r="N4" s="138"/>
-      <c r="O4" s="225">
+      <c r="O4" s="157">
         <f t="shared" si="0"/>
         <v>236872.981646</v>
       </c>
@@ -5446,21 +4843,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="224">
+        <v>126</v>
+      </c>
+      <c r="D5" s="156">
         <v>15.857766</v>
       </c>
-      <c r="E5" s="226"/>
+      <c r="E5" s="158"/>
       <c r="F5" s="136"/>
       <c r="G5" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H5" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I5" s="137"/>
       <c r="J5" s="138"/>
@@ -5468,7 +4865,7 @@
       <c r="L5" s="133"/>
       <c r="M5" s="138"/>
       <c r="N5" s="138"/>
-      <c r="O5" s="225">
+      <c r="O5" s="157">
         <f t="shared" si="0"/>
         <v>213017.37067800001</v>
       </c>
@@ -5496,21 +4893,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="224">
+        <v>128</v>
+      </c>
+      <c r="D6" s="156">
         <v>38.137878999999998</v>
       </c>
-      <c r="E6" s="226"/>
+      <c r="E6" s="158"/>
       <c r="F6" s="136"/>
       <c r="G6" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H6" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I6" s="137"/>
       <c r="J6" s="138"/>
@@ -5518,7 +4915,7 @@
       <c r="L6" s="133"/>
       <c r="M6" s="138"/>
       <c r="N6" s="138"/>
-      <c r="O6" s="225">
+      <c r="O6" s="157">
         <f t="shared" si="0"/>
         <v>512306.12860699999</v>
       </c>
@@ -5549,18 +4946,18 @@
         <v>120</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D7" s="224">
+        <v>129</v>
+      </c>
+      <c r="D7" s="156">
         <v>34.166430999999996</v>
       </c>
-      <c r="E7" s="226"/>
+      <c r="E7" s="158"/>
       <c r="F7" s="136"/>
       <c r="G7" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H7" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I7" s="137"/>
       <c r="J7" s="138"/>
@@ -5568,7 +4965,7 @@
       <c r="L7" s="133"/>
       <c r="M7" s="138"/>
       <c r="N7" s="138"/>
-      <c r="O7" s="225">
+      <c r="O7" s="157">
         <f t="shared" si="0"/>
         <v>458957.66762299993</v>
       </c>
@@ -5599,18 +4996,18 @@
         <v>116</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="D8" s="224">
+        <v>130</v>
+      </c>
+      <c r="D8" s="156">
         <v>48.341991</v>
       </c>
-      <c r="E8" s="226"/>
+      <c r="E8" s="158"/>
       <c r="F8" s="136"/>
       <c r="G8" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H8" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I8" s="137"/>
       <c r="J8" s="138"/>
@@ -5618,7 +5015,7 @@
       <c r="L8" s="134"/>
       <c r="M8" s="138"/>
       <c r="N8" s="138"/>
-      <c r="O8" s="225">
+      <c r="O8" s="157">
         <f t="shared" si="0"/>
         <v>649377.96510300005</v>
       </c>
@@ -5649,18 +5046,18 @@
         <v>118</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="224">
+        <v>130</v>
+      </c>
+      <c r="D9" s="156">
         <v>48.341991</v>
       </c>
-      <c r="E9" s="226"/>
+      <c r="E9" s="158"/>
       <c r="F9" s="136"/>
       <c r="G9" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H9" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I9" s="137"/>
       <c r="J9" s="138"/>
@@ -5668,7 +5065,7 @@
       <c r="L9" s="133"/>
       <c r="M9" s="138"/>
       <c r="N9" s="138"/>
-      <c r="O9" s="225">
+      <c r="O9" s="157">
         <f t="shared" si="0"/>
         <v>649377.96510300005</v>
       </c>
@@ -5696,21 +5093,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="224">
+        <v>126</v>
+      </c>
+      <c r="D10" s="156">
         <v>15.857766</v>
       </c>
-      <c r="E10" s="226"/>
+      <c r="E10" s="158"/>
       <c r="F10" s="136"/>
       <c r="G10" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H10" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I10" s="137"/>
       <c r="J10" s="138"/>
@@ -5718,7 +5115,7 @@
       <c r="L10" s="132"/>
       <c r="M10" s="138"/>
       <c r="N10" s="138"/>
-      <c r="O10" s="225">
+      <c r="O10" s="157">
         <f t="shared" si="0"/>
         <v>213017.37067800001</v>
       </c>
@@ -5747,21 +5144,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D11" s="224">
+        <v>133</v>
+      </c>
+      <c r="D11" s="156">
         <v>16.452445999999998</v>
       </c>
-      <c r="E11" s="226"/>
+      <c r="E11" s="158"/>
       <c r="F11" s="136"/>
       <c r="G11" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H11" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I11" s="137"/>
       <c r="J11" s="138"/>
@@ -5769,7 +5166,7 @@
       <c r="L11" s="132"/>
       <c r="M11" s="138"/>
       <c r="N11" s="138"/>
-      <c r="O11" s="225">
+      <c r="O11" s="157">
         <f t="shared" si="0"/>
         <v>221005.70711799999</v>
       </c>
@@ -5797,21 +5194,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="D12" s="224">
+        <v>135</v>
+      </c>
+      <c r="D12" s="156">
         <v>53.122635000000002</v>
       </c>
-      <c r="E12" s="226"/>
+      <c r="E12" s="158"/>
       <c r="F12" s="136"/>
       <c r="G12" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H12" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I12" s="137"/>
       <c r="J12" s="138"/>
@@ -5819,7 +5216,7 @@
       <c r="L12" s="133"/>
       <c r="M12" s="138"/>
       <c r="N12" s="138"/>
-      <c r="O12" s="225">
+      <c r="O12" s="157">
         <f t="shared" si="0"/>
         <v>713596.35595500004</v>
       </c>
@@ -5847,21 +5244,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D13" s="224">
+        <v>137</v>
+      </c>
+      <c r="D13" s="156">
         <v>29.777915000000004</v>
       </c>
-      <c r="E13" s="226"/>
+      <c r="E13" s="158"/>
       <c r="F13" s="136"/>
       <c r="G13" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H13" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I13" s="137"/>
       <c r="J13" s="138"/>
@@ -5869,7 +5266,7 @@
       <c r="L13" s="133"/>
       <c r="M13" s="138"/>
       <c r="N13" s="138"/>
-      <c r="O13" s="225">
+      <c r="O13" s="157">
         <f t="shared" si="0"/>
         <v>400006.73219500005</v>
       </c>
@@ -5897,21 +5294,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="D14" s="224">
+        <v>139</v>
+      </c>
+      <c r="D14" s="156">
         <v>31.864677</v>
       </c>
-      <c r="E14" s="226"/>
+      <c r="E14" s="158"/>
       <c r="F14" s="136"/>
       <c r="G14" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H14" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H14" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I14" s="137"/>
       <c r="J14" s="138"/>
@@ -5919,7 +5316,7 @@
       <c r="L14" s="133"/>
       <c r="M14" s="138"/>
       <c r="N14" s="138"/>
-      <c r="O14" s="225">
+      <c r="O14" s="157">
         <f t="shared" si="0"/>
         <v>428038.20614100003</v>
       </c>
@@ -5947,21 +5344,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D15" s="224">
+        <v>128</v>
+      </c>
+      <c r="D15" s="156">
         <v>38.137878999999998</v>
       </c>
-      <c r="E15" s="226"/>
+      <c r="E15" s="158"/>
       <c r="F15" s="136"/>
       <c r="G15" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H15" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H15" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I15" s="137"/>
       <c r="J15" s="138"/>
@@ -5969,7 +5366,7 @@
       <c r="L15" s="155"/>
       <c r="M15" s="138"/>
       <c r="N15" s="138"/>
-      <c r="O15" s="225">
+      <c r="O15" s="157">
         <f t="shared" si="0"/>
         <v>512306.12860699999</v>
       </c>
@@ -5997,21 +5394,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D16" s="224">
+        <v>142</v>
+      </c>
+      <c r="D16" s="156">
         <v>18.118815999999999</v>
       </c>
-      <c r="E16" s="226"/>
+      <c r="E16" s="158"/>
       <c r="F16" s="136"/>
       <c r="G16" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="H16" s="227" t="s">
-        <v>245</v>
+        <v>218</v>
+      </c>
+      <c r="H16" s="159" t="s">
+        <v>221</v>
       </c>
       <c r="I16" s="137"/>
       <c r="J16" s="138"/>
@@ -6019,7 +5416,7 @@
       <c r="L16" s="133"/>
       <c r="M16" s="138"/>
       <c r="N16" s="138"/>
-      <c r="O16" s="225">
+      <c r="O16" s="157">
         <f t="shared" si="0"/>
         <v>243390.05532799999</v>
       </c>
@@ -6047,21 +5444,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D17" s="224">
+        <v>144</v>
+      </c>
+      <c r="D17" s="156">
         <v>16.966723999999999</v>
       </c>
-      <c r="E17" s="226"/>
+      <c r="E17" s="158"/>
       <c r="F17" s="136"/>
       <c r="G17" s="137" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="I17" s="137"/>
       <c r="J17" s="138"/>
@@ -6069,7 +5466,7 @@
       <c r="L17" s="133"/>
       <c r="M17" s="138"/>
       <c r="N17" s="138"/>
-      <c r="O17" s="225">
+      <c r="O17" s="157">
         <f t="shared" si="0"/>
         <v>227914.00349199999</v>
       </c>
@@ -6097,21 +5494,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="224">
+        <v>133</v>
+      </c>
+      <c r="D18" s="156">
         <v>16.452445999999998</v>
       </c>
-      <c r="E18" s="226"/>
+      <c r="E18" s="158"/>
       <c r="F18" s="136"/>
       <c r="G18" s="137" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="I18" s="137"/>
       <c r="J18" s="138"/>
@@ -6119,7 +5516,7 @@
       <c r="L18" s="133"/>
       <c r="M18" s="138"/>
       <c r="N18" s="138"/>
-      <c r="O18" s="225">
+      <c r="O18" s="157">
         <f t="shared" si="0"/>
         <v>221005.70711799999</v>
       </c>
@@ -6147,21 +5544,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="D19" s="224">
+        <v>147</v>
+      </c>
+      <c r="D19" s="156">
         <v>27.092148999999996</v>
       </c>
-      <c r="E19" s="226"/>
+      <c r="E19" s="158"/>
       <c r="F19" s="136"/>
       <c r="G19" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H19" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I19" s="137"/>
       <c r="J19" s="138"/>
@@ -6169,7 +5566,7 @@
       <c r="L19" s="133"/>
       <c r="M19" s="138"/>
       <c r="N19" s="138"/>
-      <c r="O19" s="225">
+      <c r="O19" s="157">
         <f t="shared" si="0"/>
         <v>363928.83751699992</v>
       </c>
@@ -6197,21 +5594,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D20" s="224">
+        <v>126</v>
+      </c>
+      <c r="D20" s="156">
         <v>15.857766</v>
       </c>
-      <c r="E20" s="226"/>
+      <c r="E20" s="158"/>
       <c r="F20" s="136"/>
       <c r="G20" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H20" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I20" s="137"/>
       <c r="J20" s="138"/>
@@ -6219,7 +5616,7 @@
       <c r="L20" s="133"/>
       <c r="M20" s="138"/>
       <c r="N20" s="138"/>
-      <c r="O20" s="225">
+      <c r="O20" s="157">
         <f t="shared" si="0"/>
         <v>213017.37067800001</v>
       </c>
@@ -6246,21 +5643,21 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D21" s="224">
+        <v>150</v>
+      </c>
+      <c r="D21" s="156">
         <v>22.488373999999997</v>
       </c>
-      <c r="E21" s="226"/>
+      <c r="E21" s="158"/>
       <c r="F21" s="136"/>
       <c r="G21" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H21" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I21" s="137"/>
       <c r="J21" s="138"/>
@@ -6268,7 +5665,7 @@
       <c r="L21" s="133"/>
       <c r="M21" s="138"/>
       <c r="N21" s="138"/>
-      <c r="O21" s="225">
+      <c r="O21" s="157">
         <f t="shared" si="0"/>
         <v>302086.32794199995</v>
       </c>
@@ -6296,21 +5693,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D22" s="224">
+        <v>142</v>
+      </c>
+      <c r="D22" s="156">
         <v>18.118815999999999</v>
       </c>
-      <c r="E22" s="226"/>
+      <c r="E22" s="158"/>
       <c r="F22" s="136"/>
       <c r="G22" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H22" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I22" s="137"/>
       <c r="J22" s="138"/>
@@ -6318,7 +5715,7 @@
       <c r="L22" s="133"/>
       <c r="M22" s="138"/>
       <c r="N22" s="138"/>
-      <c r="O22" s="225">
+      <c r="O22" s="157">
         <f t="shared" si="0"/>
         <v>243390.05532799999</v>
       </c>
@@ -6346,21 +5743,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D23" s="224">
+        <v>122</v>
+      </c>
+      <c r="D23" s="156">
         <v>17.633662000000001</v>
       </c>
-      <c r="E23" s="226"/>
+      <c r="E23" s="158"/>
       <c r="F23" s="136"/>
       <c r="G23" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H23" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I23" s="137"/>
       <c r="J23" s="138"/>
@@ -6368,7 +5765,7 @@
       <c r="L23" s="133"/>
       <c r="M23" s="138"/>
       <c r="N23" s="138"/>
-      <c r="O23" s="225">
+      <c r="O23" s="157">
         <f t="shared" si="0"/>
         <v>236872.981646</v>
       </c>
@@ -6396,21 +5793,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D24" s="224">
+        <v>154</v>
+      </c>
+      <c r="D24" s="156">
         <v>24.700088999999998</v>
       </c>
-      <c r="E24" s="226"/>
+      <c r="E24" s="158"/>
       <c r="F24" s="136"/>
       <c r="G24" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H24" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I24" s="137"/>
       <c r="J24" s="138"/>
@@ -6418,7 +5815,7 @@
       <c r="L24" s="133"/>
       <c r="M24" s="138"/>
       <c r="N24" s="138"/>
-      <c r="O24" s="225">
+      <c r="O24" s="157">
         <f t="shared" si="0"/>
         <v>331796.295537</v>
       </c>
@@ -6449,18 +5846,18 @@
         <v>119</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="D25" s="224">
+        <v>155</v>
+      </c>
+      <c r="D25" s="156">
         <v>27.249818999999999</v>
       </c>
-      <c r="E25" s="226"/>
+      <c r="E25" s="158"/>
       <c r="F25" s="136"/>
       <c r="G25" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H25" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I25" s="137"/>
       <c r="J25" s="138"/>
@@ -6468,7 +5865,7 @@
       <c r="L25" s="133"/>
       <c r="M25" s="138"/>
       <c r="N25" s="138"/>
-      <c r="O25" s="225">
+      <c r="O25" s="157">
         <f t="shared" si="0"/>
         <v>366046.81862699997</v>
       </c>
@@ -6496,21 +5893,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D26" s="224">
+        <v>150</v>
+      </c>
+      <c r="D26" s="156">
         <v>22.488373999999997</v>
       </c>
-      <c r="E26" s="226"/>
+      <c r="E26" s="158"/>
       <c r="F26" s="136"/>
       <c r="G26" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H26" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I26" s="137"/>
       <c r="J26" s="138"/>
@@ -6518,7 +5915,7 @@
       <c r="L26" s="133"/>
       <c r="M26" s="138"/>
       <c r="N26" s="138"/>
-      <c r="O26" s="225">
+      <c r="O26" s="157">
         <f t="shared" si="0"/>
         <v>302086.32794199995</v>
       </c>
@@ -6546,21 +5943,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D27" s="224">
+        <v>158</v>
+      </c>
+      <c r="D27" s="156">
         <v>21.096916</v>
       </c>
-      <c r="E27" s="226"/>
+      <c r="E27" s="158"/>
       <c r="F27" s="136"/>
       <c r="G27" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H27" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I27" s="137"/>
       <c r="J27" s="138"/>
@@ -6568,7 +5965,7 @@
       <c r="L27" s="134"/>
       <c r="M27" s="138"/>
       <c r="N27" s="138"/>
-      <c r="O27" s="225">
+      <c r="O27" s="157">
         <f t="shared" si="0"/>
         <v>283394.87262799998</v>
       </c>
@@ -6596,21 +5993,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D28" s="224">
+        <v>160</v>
+      </c>
+      <c r="D28" s="156">
         <v>35.845216999999991</v>
       </c>
-      <c r="E28" s="226"/>
+      <c r="E28" s="158"/>
       <c r="F28" s="136"/>
       <c r="G28" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H28" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I28" s="137"/>
       <c r="J28" s="138"/>
@@ -6618,7 +6015,7 @@
       <c r="L28" s="134"/>
       <c r="M28" s="138"/>
       <c r="N28" s="138"/>
-      <c r="O28" s="225">
+      <c r="O28" s="157">
         <f t="shared" si="0"/>
         <v>481508.79996099987</v>
       </c>
@@ -6646,21 +6043,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D29" s="224">
+        <v>144</v>
+      </c>
+      <c r="D29" s="156">
         <v>16.966723999999999</v>
       </c>
-      <c r="E29" s="226"/>
+      <c r="E29" s="158"/>
       <c r="F29" s="136"/>
       <c r="G29" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H29" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I29" s="137"/>
       <c r="J29" s="138"/>
@@ -6668,7 +6065,7 @@
       <c r="L29" s="133"/>
       <c r="M29" s="138"/>
       <c r="N29" s="138"/>
-      <c r="O29" s="225">
+      <c r="O29" s="157">
         <f t="shared" si="0"/>
         <v>227914.00349199999</v>
       </c>
@@ -6696,21 +6093,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="D30" s="224">
+        <v>139</v>
+      </c>
+      <c r="D30" s="156">
         <v>31.864677</v>
       </c>
-      <c r="E30" s="226"/>
+      <c r="E30" s="158"/>
       <c r="F30" s="136"/>
       <c r="G30" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H30" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I30" s="137"/>
       <c r="J30" s="138"/>
@@ -6718,7 +6115,7 @@
       <c r="L30" s="133"/>
       <c r="M30" s="138"/>
       <c r="N30" s="138"/>
-      <c r="O30" s="225">
+      <c r="O30" s="157">
         <f t="shared" si="0"/>
         <v>428038.20614100003</v>
       </c>
@@ -6746,21 +6143,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D31" s="224">
+        <v>144</v>
+      </c>
+      <c r="D31" s="156">
         <v>16.966723999999999</v>
       </c>
-      <c r="E31" s="226"/>
+      <c r="E31" s="158"/>
       <c r="F31" s="136"/>
       <c r="G31" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H31" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I31" s="137"/>
       <c r="J31" s="138"/>
@@ -6768,7 +6165,7 @@
       <c r="L31" s="133"/>
       <c r="M31" s="138"/>
       <c r="N31" s="138"/>
-      <c r="O31" s="225">
+      <c r="O31" s="157">
         <f t="shared" si="0"/>
         <v>227914.00349199999</v>
       </c>
@@ -6796,21 +6193,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="D32" s="224">
+        <v>139</v>
+      </c>
+      <c r="D32" s="156">
         <v>31.864677</v>
       </c>
-      <c r="E32" s="226"/>
+      <c r="E32" s="158"/>
       <c r="F32" s="136"/>
       <c r="G32" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H32" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I32" s="137"/>
       <c r="J32" s="138"/>
@@ -6818,7 +6215,7 @@
       <c r="L32" s="133"/>
       <c r="M32" s="138"/>
       <c r="N32" s="138"/>
-      <c r="O32" s="225">
+      <c r="O32" s="157">
         <f t="shared" si="0"/>
         <v>428038.20614100003</v>
       </c>
@@ -6846,21 +6243,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D33" s="224">
+        <v>133</v>
+      </c>
+      <c r="D33" s="156">
         <v>16.452445999999998</v>
       </c>
-      <c r="E33" s="226"/>
+      <c r="E33" s="158"/>
       <c r="F33" s="136"/>
       <c r="G33" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H33" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I33" s="137"/>
       <c r="J33" s="138"/>
@@ -6868,7 +6265,7 @@
       <c r="L33" s="133"/>
       <c r="M33" s="138"/>
       <c r="N33" s="138"/>
-      <c r="O33" s="225">
+      <c r="O33" s="157">
         <f t="shared" si="0"/>
         <v>221005.70711799999</v>
       </c>
@@ -6896,21 +6293,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D34" s="224">
+        <v>144</v>
+      </c>
+      <c r="D34" s="156">
         <v>16.966723999999999</v>
       </c>
-      <c r="E34" s="226"/>
+      <c r="E34" s="158"/>
       <c r="F34" s="136"/>
       <c r="G34" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H34" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I34" s="137"/>
       <c r="J34" s="138"/>
@@ -6918,7 +6315,7 @@
       <c r="L34" s="133"/>
       <c r="M34" s="138"/>
       <c r="N34" s="138"/>
-      <c r="O34" s="225">
+      <c r="O34" s="157">
         <f t="shared" si="0"/>
         <v>227914.00349199999</v>
       </c>
@@ -6946,21 +6343,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D35" s="224">
+        <v>160</v>
+      </c>
+      <c r="D35" s="156">
         <v>35.845216999999991</v>
       </c>
-      <c r="E35" s="226"/>
+      <c r="E35" s="158"/>
       <c r="F35" s="136"/>
       <c r="G35" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H35" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I35" s="137"/>
       <c r="J35" s="138"/>
@@ -6968,7 +6365,7 @@
       <c r="L35" s="133"/>
       <c r="M35" s="138"/>
       <c r="N35" s="138"/>
-      <c r="O35" s="225">
+      <c r="O35" s="157">
         <f t="shared" si="0"/>
         <v>481508.79996099987</v>
       </c>
@@ -6996,21 +6393,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="D36" s="224">
+        <v>135</v>
+      </c>
+      <c r="D36" s="156">
         <v>53.122635000000002</v>
       </c>
-      <c r="E36" s="226"/>
+      <c r="E36" s="158"/>
       <c r="F36" s="136"/>
       <c r="G36" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H36" s="136" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="I36" s="137"/>
       <c r="J36" s="138"/>
@@ -7018,7 +6415,7 @@
       <c r="L36" s="133"/>
       <c r="M36" s="138"/>
       <c r="N36" s="138"/>
-      <c r="O36" s="225">
+      <c r="O36" s="157">
         <f t="shared" si="0"/>
         <v>713596.35595500004</v>
       </c>
@@ -7046,21 +6443,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" s="224">
+        <v>170</v>
+      </c>
+      <c r="D37" s="156">
         <v>46.468620999999999</v>
       </c>
-      <c r="E37" s="226"/>
+      <c r="E37" s="158"/>
       <c r="F37" s="136"/>
       <c r="G37" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H37" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H37" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I37" s="137"/>
       <c r="J37" s="138"/>
@@ -7068,7 +6465,7 @@
       <c r="L37" s="133"/>
       <c r="M37" s="138"/>
       <c r="N37" s="138"/>
-      <c r="O37" s="225">
+      <c r="O37" s="157">
         <f t="shared" si="0"/>
         <v>624212.98589300003</v>
       </c>
@@ -7096,21 +6493,21 @@
         <v>37</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D38" s="224">
+        <v>150</v>
+      </c>
+      <c r="D38" s="156">
         <v>22.488373999999997</v>
       </c>
-      <c r="E38" s="226"/>
+      <c r="E38" s="158"/>
       <c r="F38" s="136"/>
       <c r="G38" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H38" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H38" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I38" s="137"/>
       <c r="J38" s="138"/>
@@ -7118,7 +6515,7 @@
       <c r="L38" s="133"/>
       <c r="M38" s="138"/>
       <c r="N38" s="138"/>
-      <c r="O38" s="225">
+      <c r="O38" s="157">
         <f t="shared" si="0"/>
         <v>302086.32794199995</v>
       </c>
@@ -7146,21 +6543,21 @@
         <v>38</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D39" s="224">
+        <v>150</v>
+      </c>
+      <c r="D39" s="156">
         <v>22.488373999999997</v>
       </c>
-      <c r="E39" s="226"/>
+      <c r="E39" s="158"/>
       <c r="F39" s="136"/>
       <c r="G39" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H39" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H39" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I39" s="137"/>
       <c r="J39" s="138"/>
@@ -7168,7 +6565,7 @@
       <c r="L39" s="133"/>
       <c r="M39" s="138"/>
       <c r="N39" s="138"/>
-      <c r="O39" s="225">
+      <c r="O39" s="157">
         <f t="shared" si="0"/>
         <v>302086.32794199995</v>
       </c>
@@ -7196,21 +6593,21 @@
         <v>39</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D40" s="224">
+        <v>150</v>
+      </c>
+      <c r="D40" s="156">
         <v>22.488373999999997</v>
       </c>
-      <c r="E40" s="226"/>
+      <c r="E40" s="158"/>
       <c r="F40" s="136"/>
       <c r="G40" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H40" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H40" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I40" s="137"/>
       <c r="J40" s="138"/>
@@ -7218,7 +6615,7 @@
       <c r="L40" s="133"/>
       <c r="M40" s="138"/>
       <c r="N40" s="138"/>
-      <c r="O40" s="225">
+      <c r="O40" s="157">
         <f t="shared" si="0"/>
         <v>302086.32794199995</v>
       </c>
@@ -7246,21 +6643,21 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="D41" s="224">
+        <v>175</v>
+      </c>
+      <c r="D41" s="156">
         <v>39.622447000000008</v>
       </c>
-      <c r="E41" s="226"/>
+      <c r="E41" s="158"/>
       <c r="F41" s="136"/>
       <c r="G41" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H41" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H41" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I41" s="137"/>
       <c r="J41" s="138"/>
@@ -7268,7 +6665,7 @@
       <c r="L41" s="133"/>
       <c r="M41" s="138"/>
       <c r="N41" s="138"/>
-      <c r="O41" s="225">
+      <c r="O41" s="157">
         <f t="shared" si="0"/>
         <v>532248.33055100008</v>
       </c>
@@ -7296,21 +6693,21 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D42" s="224">
+        <v>142</v>
+      </c>
+      <c r="D42" s="156">
         <v>18.118815999999999</v>
       </c>
-      <c r="E42" s="226"/>
+      <c r="E42" s="158"/>
       <c r="F42" s="136"/>
       <c r="G42" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H42" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H42" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I42" s="137"/>
       <c r="J42" s="138"/>
@@ -7318,7 +6715,7 @@
       <c r="L42" s="133"/>
       <c r="M42" s="138"/>
       <c r="N42" s="138"/>
-      <c r="O42" s="225">
+      <c r="O42" s="157">
         <f t="shared" si="0"/>
         <v>243390.05532799999</v>
       </c>
@@ -7346,21 +6743,21 @@
         <v>42</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D43" s="224">
+        <v>178</v>
+      </c>
+      <c r="D43" s="156">
         <v>36.585352999999998</v>
       </c>
-      <c r="E43" s="226"/>
+      <c r="E43" s="158"/>
       <c r="F43" s="136"/>
       <c r="G43" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H43" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H43" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I43" s="137"/>
       <c r="J43" s="138"/>
@@ -7368,7 +6765,7 @@
       <c r="L43" s="133"/>
       <c r="M43" s="138"/>
       <c r="N43" s="138"/>
-      <c r="O43" s="225">
+      <c r="O43" s="157">
         <f t="shared" si="0"/>
         <v>491451.04684899998</v>
       </c>
@@ -7396,21 +6793,21 @@
         <v>43</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="D44" s="224">
+        <v>180</v>
+      </c>
+      <c r="D44" s="156">
         <v>27.860022999999998</v>
       </c>
-      <c r="E44" s="226"/>
+      <c r="E44" s="158"/>
       <c r="F44" s="136"/>
       <c r="G44" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H44" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H44" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I44" s="137"/>
       <c r="J44" s="138"/>
@@ -7418,7 +6815,7 @@
       <c r="L44" s="153"/>
       <c r="M44" s="138"/>
       <c r="N44" s="138"/>
-      <c r="O44" s="225">
+      <c r="O44" s="157">
         <f t="shared" si="0"/>
         <v>374243.68895899999</v>
       </c>
@@ -7446,21 +6843,21 @@
         <v>44</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D45" s="224">
+        <v>142</v>
+      </c>
+      <c r="D45" s="156">
         <v>18.118815999999999</v>
       </c>
-      <c r="E45" s="226"/>
+      <c r="E45" s="158"/>
       <c r="F45" s="136"/>
       <c r="G45" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H45" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H45" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I45" s="137"/>
       <c r="J45" s="138"/>
@@ -7468,7 +6865,7 @@
       <c r="L45" s="133"/>
       <c r="M45" s="138"/>
       <c r="N45" s="138"/>
-      <c r="O45" s="225">
+      <c r="O45" s="157">
         <f t="shared" si="0"/>
         <v>243390.05532799999</v>
       </c>
@@ -7496,21 +6893,21 @@
         <v>45</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D46" s="224">
+        <v>137</v>
+      </c>
+      <c r="D46" s="156">
         <v>29.777915000000004</v>
       </c>
-      <c r="E46" s="226"/>
+      <c r="E46" s="158"/>
       <c r="F46" s="136"/>
       <c r="G46" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H46" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H46" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I46" s="137"/>
       <c r="J46" s="138"/>
@@ -7518,7 +6915,7 @@
       <c r="L46" s="133"/>
       <c r="M46" s="138"/>
       <c r="N46" s="138"/>
-      <c r="O46" s="225">
+      <c r="O46" s="157">
         <f t="shared" si="0"/>
         <v>400006.73219500005</v>
       </c>
@@ -7546,21 +6943,21 @@
         <v>46</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D47" s="224">
+        <v>184</v>
+      </c>
+      <c r="D47" s="156">
         <v>34.166430999999996</v>
       </c>
-      <c r="E47" s="226"/>
+      <c r="E47" s="158"/>
       <c r="F47" s="136"/>
       <c r="G47" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H47" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H47" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I47" s="137"/>
       <c r="J47" s="138"/>
@@ -7568,7 +6965,7 @@
       <c r="L47" s="133"/>
       <c r="M47" s="138"/>
       <c r="N47" s="138"/>
-      <c r="O47" s="225">
+      <c r="O47" s="157">
         <f t="shared" si="0"/>
         <v>458957.66762299993</v>
       </c>
@@ -7596,21 +6993,21 @@
         <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D48" s="224">
+        <v>184</v>
+      </c>
+      <c r="D48" s="156">
         <v>34.166430999999996</v>
       </c>
-      <c r="E48" s="226"/>
+      <c r="E48" s="158"/>
       <c r="F48" s="136"/>
       <c r="G48" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H48" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H48" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I48" s="137"/>
       <c r="J48" s="138"/>
@@ -7618,7 +7015,7 @@
       <c r="L48" s="132"/>
       <c r="M48" s="138"/>
       <c r="N48" s="138"/>
-      <c r="O48" s="225">
+      <c r="O48" s="157">
         <f t="shared" si="0"/>
         <v>458957.66762299993</v>
       </c>
@@ -7646,21 +7043,21 @@
         <v>48</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D49" s="224">
+        <v>137</v>
+      </c>
+      <c r="D49" s="156">
         <v>29.777915000000004</v>
       </c>
-      <c r="E49" s="226"/>
+      <c r="E49" s="158"/>
       <c r="F49" s="136"/>
       <c r="G49" s="137" t="s">
-        <v>241</v>
-      </c>
-      <c r="H49" s="227" t="s">
-        <v>243</v>
+        <v>217</v>
+      </c>
+      <c r="H49" s="159" t="s">
+        <v>219</v>
       </c>
       <c r="I49" s="137"/>
       <c r="J49" s="138"/>
@@ -7668,7 +7065,7 @@
       <c r="L49" s="133"/>
       <c r="M49" s="138"/>
       <c r="N49" s="138"/>
-      <c r="O49" s="225">
+      <c r="O49" s="157">
         <f t="shared" si="0"/>
         <v>400006.73219500005</v>
       </c>
@@ -7696,21 +7093,21 @@
         <v>49</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D50" s="224">
+        <v>158</v>
+      </c>
+      <c r="D50" s="156">
         <v>21.096916</v>
       </c>
-      <c r="E50" s="226"/>
+      <c r="E50" s="158"/>
       <c r="F50" s="136"/>
       <c r="G50" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="H50" s="227" t="s">
-        <v>245</v>
+        <v>218</v>
+      </c>
+      <c r="H50" s="159" t="s">
+        <v>221</v>
       </c>
       <c r="I50" s="137"/>
       <c r="J50" s="138"/>
@@ -7718,7 +7115,7 @@
       <c r="L50" s="133"/>
       <c r="M50" s="138"/>
       <c r="N50" s="138"/>
-      <c r="O50" s="225">
+      <c r="O50" s="157">
         <f t="shared" si="0"/>
         <v>283394.87262799998</v>
       </c>
@@ -7746,21 +7143,21 @@
         <v>50</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="D51" s="224">
+        <v>189</v>
+      </c>
+      <c r="D51" s="156">
         <v>39.59669499999999</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
       <c r="G51" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="H51" s="227" t="s">
-        <v>245</v>
+        <v>218</v>
+      </c>
+      <c r="H51" s="159" t="s">
+        <v>221</v>
       </c>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
@@ -7768,7 +7165,7 @@
       <c r="L51" s="8"/>
       <c r="M51" s="8"/>
       <c r="N51" s="8"/>
-      <c r="O51" s="225">
+      <c r="O51" s="157">
         <f t="shared" si="0"/>
         <v>531902.40393499983</v>
       </c>
@@ -7780,21 +7177,21 @@
         <v>51</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D52" s="224">
+        <v>142</v>
+      </c>
+      <c r="D52" s="156">
         <v>18.118815999999999</v>
       </c>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
       <c r="G52" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="H52" s="227" t="s">
-        <v>245</v>
+        <v>218</v>
+      </c>
+      <c r="H52" s="159" t="s">
+        <v>221</v>
       </c>
       <c r="I52" s="8"/>
       <c r="J52" s="8"/>
@@ -7802,7 +7199,7 @@
       <c r="L52" s="8"/>
       <c r="M52" s="8"/>
       <c r="N52" s="8"/>
-      <c r="O52" s="225">
+      <c r="O52" s="157">
         <f t="shared" si="0"/>
         <v>243390.05532799999</v>
       </c>
@@ -7814,21 +7211,21 @@
         <v>52</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D53" s="224">
+        <v>142</v>
+      </c>
+      <c r="D53" s="156">
         <v>18.118815999999999</v>
       </c>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
       <c r="G53" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="H53" s="227" t="s">
-        <v>245</v>
+        <v>218</v>
+      </c>
+      <c r="H53" s="159" t="s">
+        <v>221</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
@@ -7836,7 +7233,7 @@
       <c r="L53" s="8"/>
       <c r="M53" s="8"/>
       <c r="N53" s="8"/>
-      <c r="O53" s="225">
+      <c r="O53" s="157">
         <f t="shared" si="0"/>
         <v>243390.05532799999</v>
       </c>
@@ -7848,21 +7245,21 @@
         <v>53</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D54" s="224">
+        <v>129</v>
+      </c>
+      <c r="D54" s="156">
         <v>34.166430999999996</v>
       </c>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="H54" s="227" t="s">
-        <v>245</v>
+        <v>218</v>
+      </c>
+      <c r="H54" s="159" t="s">
+        <v>221</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
@@ -7870,7 +7267,7 @@
       <c r="L54" s="8"/>
       <c r="M54" s="8"/>
       <c r="N54" s="8"/>
-      <c r="O54" s="225">
+      <c r="O54" s="157">
         <f t="shared" si="0"/>
         <v>458957.66762299993</v>
       </c>
@@ -7882,21 +7279,21 @@
         <v>54</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="D55" s="224">
+        <v>194</v>
+      </c>
+      <c r="D55" s="156">
         <v>27.092148999999996</v>
       </c>
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
       <c r="G55" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="H55" s="227" t="s">
-        <v>245</v>
+        <v>218</v>
+      </c>
+      <c r="H55" s="159" t="s">
+        <v>221</v>
       </c>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
@@ -7904,7 +7301,7 @@
       <c r="L55" s="8"/>
       <c r="M55" s="8"/>
       <c r="N55" s="8"/>
-      <c r="O55" s="225">
+      <c r="O55" s="157">
         <f t="shared" si="0"/>
         <v>363928.83751699992</v>
       </c>
@@ -7916,21 +7313,21 @@
         <v>55</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D56" s="224">
+        <v>158</v>
+      </c>
+      <c r="D56" s="156">
         <v>21.096916</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
       <c r="G56" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="H56" s="227" t="s">
-        <v>245</v>
+        <v>218</v>
+      </c>
+      <c r="H56" s="159" t="s">
+        <v>221</v>
       </c>
       <c r="I56" s="8"/>
       <c r="J56" s="8"/>
@@ -7938,7 +7335,7 @@
       <c r="L56" s="8"/>
       <c r="M56" s="8"/>
       <c r="N56" s="8"/>
-      <c r="O56" s="225">
+      <c r="O56" s="157">
         <f t="shared" si="0"/>
         <v>283394.87262799998</v>
       </c>
@@ -7950,21 +7347,21 @@
         <v>56</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D57" s="224">
+        <v>142</v>
+      </c>
+      <c r="D57" s="156">
         <v>18.118815999999999</v>
       </c>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
       <c r="G57" s="137" t="s">
-        <v>242</v>
-      </c>
-      <c r="H57" s="227" t="s">
-        <v>245</v>
+        <v>218</v>
+      </c>
+      <c r="H57" s="159" t="s">
+        <v>221</v>
       </c>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
@@ -7972,7 +7369,7 @@
       <c r="L57" s="8"/>
       <c r="M57" s="8"/>
       <c r="N57" s="8"/>
-      <c r="O57" s="225">
+      <c r="O57" s="157">
         <f t="shared" si="0"/>
         <v>243390.05532799999</v>
       </c>
@@ -7984,21 +7381,21 @@
         <v>57</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D58" s="224">
+        <v>158</v>
+      </c>
+      <c r="D58" s="156">
         <v>21.096916</v>
       </c>
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
       <c r="G58" s="137" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="I58" s="8"/>
       <c r="J58" s="8"/>
@@ -8006,7 +7403,7 @@
       <c r="L58" s="8"/>
       <c r="M58" s="8"/>
       <c r="N58" s="8"/>
-      <c r="O58" s="225">
+      <c r="O58" s="157">
         <f t="shared" si="0"/>
         <v>283394.87262799998</v>
       </c>
@@ -8018,21 +7415,21 @@
         <v>58</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D59" s="224">
+        <v>158</v>
+      </c>
+      <c r="D59" s="156">
         <v>21.096916</v>
       </c>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
       <c r="G59" s="137" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="I59" s="8"/>
       <c r="J59" s="8"/>
@@ -8040,7 +7437,7 @@
       <c r="L59" s="8"/>
       <c r="M59" s="8"/>
       <c r="N59" s="8"/>
-      <c r="O59" s="225">
+      <c r="O59" s="157">
         <f t="shared" si="0"/>
         <v>283394.87262799998</v>
       </c>
@@ -8052,21 +7449,21 @@
         <v>59</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D60" s="224">
+        <v>158</v>
+      </c>
+      <c r="D60" s="156">
         <v>21.096916</v>
       </c>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
       <c r="G60" s="137" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="8"/>
@@ -8074,7 +7471,7 @@
       <c r="L60" s="8"/>
       <c r="M60" s="8"/>
       <c r="N60" s="8"/>
-      <c r="O60" s="225">
+      <c r="O60" s="157">
         <f t="shared" si="0"/>
         <v>283394.87262799998</v>
       </c>
@@ -8086,21 +7483,21 @@
         <v>60</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D61" s="224">
+        <v>201</v>
+      </c>
+      <c r="D61" s="156">
         <v>28.368053</v>
       </c>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
       <c r="G61" s="137" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="8"/>
@@ -8108,7 +7505,7 @@
       <c r="L61" s="8"/>
       <c r="M61" s="8"/>
       <c r="N61" s="8"/>
-      <c r="O61" s="225">
+      <c r="O61" s="157">
         <f t="shared" si="0"/>
         <v>381068.055949</v>
       </c>
@@ -8120,21 +7517,21 @@
         <v>61</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="D62" s="224">
+        <v>158</v>
+      </c>
+      <c r="D62" s="156">
         <v>21.096916</v>
       </c>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
       <c r="G62" s="137" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
@@ -8142,7 +7539,7 @@
       <c r="L62" s="8"/>
       <c r="M62" s="8"/>
       <c r="N62" s="8"/>
-      <c r="O62" s="225">
+      <c r="O62" s="157">
         <f t="shared" si="0"/>
         <v>283394.87262799998</v>
       </c>
@@ -8154,21 +7551,21 @@
         <v>62</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D63" s="224">
+        <v>184</v>
+      </c>
+      <c r="D63" s="156">
         <v>34.166430999999996</v>
       </c>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
       <c r="G63" s="137" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="I63" s="8"/>
       <c r="J63" s="8"/>
@@ -8176,7 +7573,7 @@
       <c r="L63" s="8"/>
       <c r="M63" s="8"/>
       <c r="N63" s="8"/>
-      <c r="O63" s="225">
+      <c r="O63" s="157">
         <f t="shared" si="0"/>
         <v>458957.66762299993</v>
       </c>
@@ -8188,21 +7585,21 @@
         <v>63</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D64" s="224">
+        <v>142</v>
+      </c>
+      <c r="D64" s="156">
         <v>18.118815999999999</v>
       </c>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
       <c r="G64" s="137" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
@@ -8210,7 +7607,7 @@
       <c r="L64" s="8"/>
       <c r="M64" s="8"/>
       <c r="N64" s="8"/>
-      <c r="O64" s="225">
+      <c r="O64" s="157">
         <f t="shared" si="0"/>
         <v>243390.05532799999</v>
       </c>
@@ -8222,21 +7619,21 @@
         <v>64</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="D65" s="224">
+        <v>206</v>
+      </c>
+      <c r="D65" s="156">
         <v>36.585352999999998</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
       <c r="G65" s="137" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="8"/>
@@ -8244,7 +7641,7 @@
       <c r="L65" s="8"/>
       <c r="M65" s="8"/>
       <c r="N65" s="8"/>
-      <c r="O65" s="225">
+      <c r="O65" s="157">
         <f t="shared" si="0"/>
         <v>491451.04684899998</v>
       </c>
@@ -8259,18 +7656,18 @@
         <v>86</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D66" s="224">
+        <v>207</v>
+      </c>
+      <c r="D66" s="156">
         <v>53.238641000000001</v>
       </c>
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
       <c r="G66" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H66" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
@@ -8278,7 +7675,7 @@
       <c r="L66" s="8"/>
       <c r="M66" s="8"/>
       <c r="N66" s="8"/>
-      <c r="O66" s="225">
+      <c r="O66" s="157">
         <f t="shared" si="0"/>
         <v>715154.66455300001</v>
       </c>
@@ -8290,21 +7687,21 @@
         <v>66</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D67" s="224">
+        <v>144</v>
+      </c>
+      <c r="D67" s="156">
         <v>16.966723999999999</v>
       </c>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
       <c r="G67" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H67" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I67" s="8"/>
       <c r="J67" s="8"/>
@@ -8312,7 +7709,7 @@
       <c r="L67" s="8"/>
       <c r="M67" s="8"/>
       <c r="N67" s="8"/>
-      <c r="O67" s="225">
+      <c r="O67" s="157">
         <f t="shared" ref="O67:O72" si="2">D67*13433</f>
         <v>227914.00349199999</v>
       </c>
@@ -8324,21 +7721,21 @@
         <v>67</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D68" s="224">
+        <v>160</v>
+      </c>
+      <c r="D68" s="156">
         <v>35.845216999999991</v>
       </c>
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
       <c r="G68" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H68" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
@@ -8346,7 +7743,7 @@
       <c r="L68" s="8"/>
       <c r="M68" s="8"/>
       <c r="N68" s="8"/>
-      <c r="O68" s="225">
+      <c r="O68" s="157">
         <f t="shared" si="2"/>
         <v>481508.79996099987</v>
       </c>
@@ -8358,21 +7755,21 @@
         <v>68</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D69" s="224">
+        <v>122</v>
+      </c>
+      <c r="D69" s="156">
         <v>17.633662000000001</v>
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
       <c r="G69" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H69" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I69" s="8"/>
       <c r="J69" s="8"/>
@@ -8380,7 +7777,7 @@
       <c r="L69" s="8"/>
       <c r="M69" s="8"/>
       <c r="N69" s="8"/>
-      <c r="O69" s="225">
+      <c r="O69" s="157">
         <f t="shared" si="2"/>
         <v>236872.981646</v>
       </c>
@@ -8395,18 +7792,18 @@
         <v>117</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D70" s="224">
+        <v>160</v>
+      </c>
+      <c r="D70" s="156">
         <v>35.845216999999991</v>
       </c>
       <c r="E70" s="8"/>
       <c r="F70" s="8"/>
       <c r="G70" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H70" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
@@ -8414,7 +7811,7 @@
       <c r="L70" s="8"/>
       <c r="M70" s="8"/>
       <c r="N70" s="8"/>
-      <c r="O70" s="225">
+      <c r="O70" s="157">
         <f t="shared" si="2"/>
         <v>481508.79996099987</v>
       </c>
@@ -8426,21 +7823,21 @@
         <v>70</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="D71" s="224">
+        <v>212</v>
+      </c>
+      <c r="D71" s="156">
         <v>41.832876999999996</v>
       </c>
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
       <c r="G71" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H71" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I71" s="8"/>
       <c r="J71" s="8"/>
@@ -8448,7 +7845,7 @@
       <c r="L71" s="8"/>
       <c r="M71" s="8"/>
       <c r="N71" s="8"/>
-      <c r="O71" s="225">
+      <c r="O71" s="157">
         <f t="shared" si="2"/>
         <v>561941.0367409999</v>
       </c>
@@ -8460,21 +7857,21 @@
         <v>71</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D72" s="224">
+        <v>170</v>
+      </c>
+      <c r="D72" s="156">
         <v>46.468620999999999</v>
       </c>
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
       <c r="G72" s="137" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="H72" s="154" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
@@ -8482,7 +7879,7 @@
       <c r="L72" s="8"/>
       <c r="M72" s="8"/>
       <c r="N72" s="8"/>
-      <c r="O72" s="225">
+      <c r="O72" s="157">
         <f t="shared" si="2"/>
         <v>624212.98589300003</v>
       </c>
@@ -8490,40 +7887,40 @@
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="B2:B32">
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J2:J50 M2:N50">
-    <cfRule type="containsText" dxfId="9" priority="78" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="8" priority="78" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J50">
-    <cfRule type="containsText" dxfId="8" priority="51" operator="containsText" text="WIP">
+    <cfRule type="containsText" dxfId="7" priority="51" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="56" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="6" priority="56" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="57" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="5" priority="57" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N50 J2:J50">
-    <cfRule type="containsText" dxfId="5" priority="77" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="4" priority="77" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N50">
-    <cfRule type="containsText" dxfId="4" priority="75" operator="containsText" text="Complete">
+    <cfRule type="containsText" dxfId="3" priority="75" operator="containsText" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",M2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="76" operator="containsText" text="ROW">
+    <cfRule type="containsText" dxfId="2" priority="76" operator="containsText" text="ROW">
       <formula>NOT(ISERROR(SEARCH("ROW",M2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="167" operator="containsText" text="WIP">
+    <cfRule type="containsText" dxfId="1" priority="167" operator="containsText" text="WIP">
       <formula>NOT(ISERROR(SEARCH("WIP",M2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B32">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8532,382 +7929,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E3F0E1F-80A5-4555-9FE1-744B1DEBC4EC}">
-  <dimension ref="B1:L15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="1.26953125" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" customWidth="1"/>
-    <col min="6" max="6" width="11.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" customWidth="1"/>
-    <col min="9" max="9" width="15.1796875" customWidth="1"/>
-    <col min="10" max="10" width="11.1796875" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B1" s="216" t="s">
-        <v>121</v>
-      </c>
-      <c r="C1" s="216"/>
-      <c r="D1" s="216"/>
-      <c r="E1" s="216"/>
-      <c r="F1" s="216"/>
-      <c r="G1" s="216"/>
-      <c r="H1" s="216"/>
-      <c r="I1" s="216"/>
-      <c r="J1" s="216"/>
-      <c r="K1" s="216"/>
-      <c r="L1" s="216"/>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="217" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="217"/>
-      <c r="D2" s="217"/>
-      <c r="E2" s="217"/>
-      <c r="F2" s="217"/>
-      <c r="G2" s="217"/>
-      <c r="H2" s="217"/>
-      <c r="I2" s="217"/>
-      <c r="J2" s="217"/>
-      <c r="K2" s="217"/>
-      <c r="L2" s="217"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B3" s="218" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="218"/>
-      <c r="I3" s="218"/>
-      <c r="J3" s="218"/>
-      <c r="K3" s="218"/>
-      <c r="L3" s="218"/>
-    </row>
-    <row r="4" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="219" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="219"/>
-      <c r="D4" s="219"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="219"/>
-      <c r="G4" s="219"/>
-      <c r="H4" s="219"/>
-      <c r="I4" s="219"/>
-      <c r="J4" s="219"/>
-      <c r="K4" s="219"/>
-      <c r="L4" s="219"/>
-    </row>
-    <row r="5" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="175" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="176"/>
-      <c r="D5" s="176"/>
-      <c r="E5" s="176"/>
-      <c r="F5" s="176"/>
-      <c r="G5" s="176"/>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="177"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B6" s="212" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="210" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="210" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="210" t="s">
-        <v>127</v>
-      </c>
-      <c r="F6" s="210" t="s">
-        <v>128</v>
-      </c>
-      <c r="G6" s="210" t="s">
-        <v>129</v>
-      </c>
-      <c r="H6" s="210" t="s">
-        <v>130</v>
-      </c>
-      <c r="I6" s="210" t="s">
-        <v>131</v>
-      </c>
-      <c r="J6" s="210" t="s">
-        <v>132</v>
-      </c>
-      <c r="K6" s="214" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B7" s="213"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="211"/>
-      <c r="E7" s="211"/>
-      <c r="F7" s="211"/>
-      <c r="G7" s="211"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="211"/>
-      <c r="K7" s="215"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B8" s="172">
-        <v>1</v>
-      </c>
-      <c r="C8" s="173" t="s">
-        <v>133</v>
-      </c>
-      <c r="D8" s="174">
-        <v>4901.2360000000008</v>
-      </c>
-      <c r="E8" s="174" t="s">
-        <v>134</v>
-      </c>
-      <c r="F8" s="174">
-        <v>13</v>
-      </c>
-      <c r="G8" s="133">
-        <v>45967</v>
-      </c>
-      <c r="H8" s="133">
-        <v>45968</v>
-      </c>
-      <c r="I8" s="133">
-        <v>45972</v>
-      </c>
-      <c r="J8" s="133">
-        <v>45974</v>
-      </c>
-      <c r="K8" s="204" t="s">
-        <v>135</v>
-      </c>
-      <c r="L8" s="156"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B9" s="164">
-        <v>2</v>
-      </c>
-      <c r="C9" s="165" t="s">
-        <v>136</v>
-      </c>
-      <c r="D9" s="135">
-        <v>4418.3890000000001</v>
-      </c>
-      <c r="E9" s="135" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="135">
-        <v>11</v>
-      </c>
-      <c r="G9" s="133">
-        <v>45977</v>
-      </c>
-      <c r="H9" s="133">
-        <v>45978</v>
-      </c>
-      <c r="I9" s="133">
-        <v>45981</v>
-      </c>
-      <c r="J9" s="133">
-        <v>45983</v>
-      </c>
-      <c r="K9" s="205"/>
-      <c r="L9" s="156"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B10" s="164">
-        <v>3</v>
-      </c>
-      <c r="C10" s="165" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="135">
-        <v>419.48</v>
-      </c>
-      <c r="E10" s="135" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" s="135">
-        <v>1</v>
-      </c>
-      <c r="G10" s="133">
-        <v>45984</v>
-      </c>
-      <c r="H10" s="133">
-        <v>45985</v>
-      </c>
-      <c r="I10" s="133">
-        <v>45988</v>
-      </c>
-      <c r="J10" s="133">
-        <v>45990</v>
-      </c>
-      <c r="K10" s="206"/>
-      <c r="L10" s="156"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B11" s="163">
-        <v>4</v>
-      </c>
-      <c r="C11" s="157" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="8">
-        <v>840.43900000000008</v>
-      </c>
-      <c r="E11" s="166" t="s">
-        <v>134</v>
-      </c>
-      <c r="F11" s="8">
-        <v>2</v>
-      </c>
-      <c r="G11" s="133">
-        <v>45971</v>
-      </c>
-      <c r="H11" s="133">
-        <v>45973</v>
-      </c>
-      <c r="I11" s="133">
-        <v>45976</v>
-      </c>
-      <c r="J11" s="133">
-        <v>45979</v>
-      </c>
-      <c r="K11" s="207" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="163">
-        <v>5</v>
-      </c>
-      <c r="C12" s="157" t="s">
-        <v>140</v>
-      </c>
-      <c r="D12" s="8">
-        <v>3283.51</v>
-      </c>
-      <c r="E12" s="166" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="8">
-        <v>8</v>
-      </c>
-      <c r="G12" s="133">
-        <v>45983</v>
-      </c>
-      <c r="H12" s="133">
-        <v>45984</v>
-      </c>
-      <c r="I12" s="133">
-        <v>45987</v>
-      </c>
-      <c r="J12" s="133">
-        <v>45989</v>
-      </c>
-      <c r="K12" s="208"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B13" s="163">
-        <v>6</v>
-      </c>
-      <c r="C13" s="157" t="s">
-        <v>141</v>
-      </c>
-      <c r="D13" s="8">
-        <v>4049.7639999999997</v>
-      </c>
-      <c r="E13" s="166" t="s">
-        <v>134</v>
-      </c>
-      <c r="F13" s="8">
-        <v>10</v>
-      </c>
-      <c r="G13" s="133">
-        <v>45988</v>
-      </c>
-      <c r="H13" s="133">
-        <f>G13+1</f>
-        <v>45989</v>
-      </c>
-      <c r="I13" s="133">
-        <v>45991</v>
-      </c>
-      <c r="J13" s="133">
-        <v>45995</v>
-      </c>
-      <c r="K13" s="209"/>
-    </row>
-    <row r="14" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="168"/>
-      <c r="C14" s="169"/>
-      <c r="D14" s="169"/>
-      <c r="E14" s="170"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="92"/>
-      <c r="H14" s="92"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="92"/>
-      <c r="K14" s="171"/>
-    </row>
-    <row r="15" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="159" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="160"/>
-      <c r="D15" s="167">
-        <v>17.912817999999998</v>
-      </c>
-      <c r="E15" s="161"/>
-      <c r="F15" s="162">
-        <v>45</v>
-      </c>
-      <c r="G15" s="162"/>
-      <c r="H15" s="162"/>
-      <c r="I15" s="162"/>
-      <c r="J15" s="162"/>
-      <c r="K15" s="158"/>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:L3"/>
-    <mergeCell ref="B4:L4"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="K6:K7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21CFCD75-33F5-49B3-A4C8-4F19BD2235FD}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9175,118 +8196,118 @@
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="181" t="s">
+      <c r="A18" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="181" t="s">
+      <c r="B18" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="178" t="s">
+      <c r="C18" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="178" t="s">
+      <c r="D18" s="174" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="181" t="s">
+      <c r="E18" s="178" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="193" t="s">
+      <c r="F18" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="193"/>
-      <c r="H18" s="193"/>
-      <c r="I18" s="193"/>
-      <c r="J18" s="193"/>
-      <c r="K18" s="186" t="s">
+      <c r="G18" s="165"/>
+      <c r="H18" s="165"/>
+      <c r="I18" s="165"/>
+      <c r="J18" s="165"/>
+      <c r="K18" s="168" t="s">
         <v>19</v>
       </c>
-      <c r="M18" s="178" t="s">
+      <c r="M18" s="174" t="s">
         <v>36</v>
       </c>
-      <c r="O18" s="187" t="s">
+      <c r="O18" s="169" t="s">
         <v>31</v>
       </c>
-      <c r="P18" s="188"/>
-      <c r="Q18" s="188"/>
-      <c r="R18" s="188"/>
-      <c r="S18" s="188"/>
-      <c r="T18" s="189"/>
-      <c r="V18" s="187" t="s">
+      <c r="P18" s="170"/>
+      <c r="Q18" s="170"/>
+      <c r="R18" s="170"/>
+      <c r="S18" s="170"/>
+      <c r="T18" s="171"/>
+      <c r="V18" s="169" t="s">
         <v>30</v>
       </c>
-      <c r="W18" s="188"/>
-      <c r="X18" s="188"/>
-      <c r="Y18" s="188"/>
-      <c r="Z18" s="188"/>
-      <c r="AA18" s="189"/>
-      <c r="AB18" s="190" t="s">
+      <c r="W18" s="170"/>
+      <c r="X18" s="170"/>
+      <c r="Y18" s="170"/>
+      <c r="Z18" s="170"/>
+      <c r="AA18" s="171"/>
+      <c r="AB18" s="172" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="182"/>
-      <c r="B19" s="182"/>
-      <c r="C19" s="179"/>
-      <c r="D19" s="182"/>
-      <c r="E19" s="182"/>
-      <c r="F19" s="221" t="s">
+      <c r="A19" s="179"/>
+      <c r="B19" s="179"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="179"/>
+      <c r="E19" s="179"/>
+      <c r="F19" s="186" t="s">
         <v>40</v>
       </c>
-      <c r="G19" s="222" t="s">
+      <c r="G19" s="187" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="223"/>
-      <c r="I19" s="222" t="s">
+      <c r="H19" s="188"/>
+      <c r="I19" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="J19" s="223"/>
-      <c r="K19" s="186"/>
-      <c r="M19" s="192"/>
-      <c r="O19" s="184" t="s">
+      <c r="J19" s="188"/>
+      <c r="K19" s="168"/>
+      <c r="M19" s="175"/>
+      <c r="O19" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="P19" s="184" t="s">
+      <c r="P19" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="Q19" s="184" t="s">
+      <c r="Q19" s="166" t="s">
         <v>26</v>
       </c>
-      <c r="R19" s="184" t="s">
+      <c r="R19" s="166" t="s">
         <v>27</v>
       </c>
-      <c r="S19" s="184" t="s">
+      <c r="S19" s="166" t="s">
         <v>28</v>
       </c>
       <c r="T19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="V19" s="184" t="s">
+      <c r="V19" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="W19" s="184" t="s">
+      <c r="W19" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="X19" s="184" t="s">
+      <c r="X19" s="166" t="s">
         <v>26</v>
       </c>
-      <c r="Y19" s="184" t="s">
+      <c r="Y19" s="166" t="s">
         <v>27</v>
       </c>
-      <c r="Z19" s="184" t="s">
+      <c r="Z19" s="166" t="s">
         <v>28</v>
       </c>
       <c r="AA19" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="AB19" s="191"/>
+      <c r="AB19" s="173"/>
     </row>
     <row r="20" spans="1:28" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="182"/>
-      <c r="B20" s="182"/>
-      <c r="C20" s="179"/>
-      <c r="D20" s="182"/>
-      <c r="E20" s="182"/>
-      <c r="F20" s="221"/>
+      <c r="A20" s="179"/>
+      <c r="B20" s="179"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="179"/>
+      <c r="E20" s="179"/>
+      <c r="F20" s="186"/>
       <c r="G20" s="93" t="s">
         <v>10</v>
       </c>
@@ -9305,17 +8326,17 @@
       <c r="M20" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="O20" s="185"/>
-      <c r="P20" s="185"/>
-      <c r="Q20" s="185"/>
-      <c r="R20" s="185"/>
-      <c r="S20" s="185"/>
+      <c r="O20" s="167"/>
+      <c r="P20" s="167"/>
+      <c r="Q20" s="167"/>
+      <c r="R20" s="167"/>
+      <c r="S20" s="167"/>
       <c r="T20" s="19"/>
-      <c r="V20" s="185"/>
-      <c r="W20" s="185"/>
-      <c r="X20" s="185"/>
-      <c r="Y20" s="185"/>
-      <c r="Z20" s="185"/>
+      <c r="V20" s="167"/>
+      <c r="W20" s="167"/>
+      <c r="X20" s="167"/>
+      <c r="Y20" s="167"/>
+      <c r="Z20" s="167"/>
       <c r="AA20" s="19" t="s">
         <v>20</v>
       </c>
@@ -9336,7 +8357,7 @@
       <c r="D21" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="220" t="s">
+      <c r="E21" s="189" t="s">
         <v>99</v>
       </c>
       <c r="F21" s="113">
@@ -9410,7 +8431,7 @@
       <c r="D22" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="220"/>
+      <c r="E22" s="189"/>
       <c r="F22" s="113">
         <v>45913</v>
       </c>
@@ -9482,7 +8503,7 @@
       <c r="D23" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="220"/>
+      <c r="E23" s="189"/>
       <c r="F23" s="113">
         <v>45910</v>
       </c>
@@ -9554,7 +8575,7 @@
       <c r="D24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="220"/>
+      <c r="E24" s="189"/>
       <c r="F24" s="113">
         <v>45927</v>
       </c>
@@ -9626,7 +8647,7 @@
       <c r="D25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="220"/>
+      <c r="E25" s="189"/>
       <c r="F25" s="113">
         <v>45915</v>
       </c>
@@ -10321,6 +9342,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="E21:E25"/>
+    <mergeCell ref="W19:W20"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="M18:M19"/>
+    <mergeCell ref="O18:T18"/>
+    <mergeCell ref="V18:AA18"/>
+    <mergeCell ref="V19:V20"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
     <mergeCell ref="AB18:AB19"/>
     <mergeCell ref="F19:F20"/>
     <mergeCell ref="G19:H19"/>
@@ -10334,21 +9367,9 @@
     <mergeCell ref="Q19:Q20"/>
     <mergeCell ref="R19:R20"/>
     <mergeCell ref="S19:S20"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="E21:E25"/>
-    <mergeCell ref="W19:W20"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="M18:M19"/>
-    <mergeCell ref="O18:T18"/>
-    <mergeCell ref="V18:AA18"/>
-    <mergeCell ref="V19:V20"/>
   </mergeCells>
   <conditionalFormatting sqref="C26:C27">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="4DT6">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="4DT6">
       <formula>NOT(ISERROR(SEARCH("4DT6",C26)))</formula>
     </cfRule>
   </conditionalFormatting>
